--- a/TEST/Arhitektura_i_projektovanje.xlsx
+++ b/TEST/Arhitektura_i_projektovanje.xlsx
@@ -2,22 +2,47 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Architect" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bauberater" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Architecture firm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Architekturdesigner" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Architectural designer" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Architectural and engineering m" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Building consultant" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Building design company" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Building firm" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Log home builder" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Architekt" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Architekturbüro" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Modellbauer für Architektur und" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Architect'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bauberater'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Architecture firm'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Architekturdesigner'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Architectural designer'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Architectural and engineering m'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Building consultant'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Building design company'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Building firm'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Log home builder'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Architekt'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Architekturbüro'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Modellbauer für Architektur und'!$A$1:$Q$5</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +50,54 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006400"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,15 +105,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,91 +532,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Br.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Naziv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kategorija</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Adresa</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Telefon</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Web stranica</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Radno vrijeme</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ocjena</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Recenzije</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Plus Code</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opis</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Google Maps URL</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Datum scrape</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Pozvano (DA/NE)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Zainteresovan (DA/NE)</t>
         </is>
@@ -508,73 +645,3821 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kuhs Architekten Dipl.Ing.(FH) Winfried Kuhs</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Architekturbüro Pongratz Regensburg</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Arhitekt</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>
-Basler Str. 24 b, 79100 Freiburg im Breisgau-Süd, Njemačka</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+Dr.-Gessler-Straße 16, 93051 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>
-+49 761 287800</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ivanagrmusa2020@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://kuhs-architekten.de/</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Poslato</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
++49 941 42830</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.architekturbuero-pongratz.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Poslato (Test)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekturb%C3%BCro+Pongratz+Regensburg/data=!4m7!3m6!1s0x479fc0e459b33939:0xec7c0897acb24831!8m2!3d49.006234!4d12.063848!16s%2Fg%2F1tvw3ybm!19sChIJOTmzWeTAn0cRMUiyrJcIfOw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:43:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Doemges Architekten AG</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>
+Budapester Str. 4, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 992060</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.doemges.ag/</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Doemges+Architekten+AG/data=!4m7!3m6!1s0x479fc0e1fd8473cd:0x5ca6394ae9d138dc!8m2!3d49.0188952!4d12.121771!16s%2Fg%2F1tff20fc!19sChIJzXOE_eHAn0cR3DjR6Uo5plw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="71.25" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Huber Architekten GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>
+Dechbettener Str. 10, 93049 Regensburg-Westenviertel, Njemačka</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 595810</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>http://www.archhu.de/</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Huber+Architekten+GmbH/data=!4m7!3m6!1s0x479fc1a5c344f023:0x363bdbfeba440210!8m2!3d49.0171277!4d12.0830257!16s%2Fg%2F1tg5ymqj!19sChIJI_BEw6XBn0cREAJEuv7bOzY?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="71.25" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Fichtner Gruber Architekten</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>
+Landshuter Str. 9, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 46568111</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>http://www.fichtner-gruber.de/</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fichtner+Gruber+Architekten/data=!4m7!3m6!1s0x8758deaca857318f:0x4beac055f8bda878!8m2!3d49.0152434!4d12.1040118!16s%2Fg%2F11k9bk62n9!19sChIJjzFXqKzeWIcReKi9-FXA6ks?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="85.5" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/place/Kuhs+Architekten+Dipl.Ing.%28FH%29+Winfried+Kuhs/data=!4m7!3m6!1s0x47911b6279e88f5f:0x2e4ee915a8f34dd7!8m2!3d47.9875898!4d7.8453231!16s%2Fg%2F1tftd7gw!19sChIJX4_oeWIbkUcR103zqBXpTi4?authuser=0&amp;hl=hr&amp;rclk=1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-08-04 18:06</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-04 18:37:11</t>
-        </is>
-      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>greßmann söllner architekten gmbh</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>
+Donaulände 7, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 585270</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>http://www.gressmann-soellner.com/</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/gre%C3%9Fmann+s%C3%B6llner+architekten+gmbh/data=!4m7!3m6!1s0x479fc1a3c9798e49:0x68a305815f2ac99d!8m2!3d49.0199088!4d12.1049624!16s%2Fg%2F1tdg6syv!19sChIJSY55yaPBn0cRnckqX4EFo2g?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="71.25" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>PURE GRUPPE</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Arhitektonska tvrtka</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>
+Watmarkt 5, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 5861240000</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.puregruppe.de/</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/PURE+GRUPPE/data=!4m7!3m6!1s0x479fc1a12bb878b3:0x811be9b90bc55a40!8m2!3d49.0201388!4d12.0965148!16s%2Fg%2F1td52fgl!19sChIJs3i4K6HBn0cRQFrFC7npG4E?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="71.25" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Architekturbüro Fabi</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>
+Glockengasse 10, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 900333</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fabi-architekten.de/</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekturb%C3%BCro+Fabi/data=!4m7!3m6!1s0x479fc1a92098bb61:0x6918ec7dd73ddbea!8m2!3d49.0189912!4d12.0914993!16s%2Fg%2F1tknzsnm!19sChIJYbuYIKnBn0cR6ts9133sGGk?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="71.25" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>brandl architekten</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>
+Malergasse 10, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 5839317</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>http://www.brandl-architekten.de/</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/brandl+architekten/data=!4m7!3m6!1s0x479fc1a7ddd19c77:0x542098587a2a9738!8m2!3d49.0171096!4d12.0965561!16s%2Fg%2F1td2sx69!19sChIJd5zR3afBn0cROJcqeliYIFQ?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q9"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="bojan.mikulic@hotmail.com" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId17"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Woodtec Haus GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Voditelj projekata u razvoju nekretnina</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Donaustaufer Str. 240A, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 172 7149516</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.woodtec-haus.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Woodtec+Haus+GmbH/data=!4m7!3m6!1s0x479fc18af4faa13b:0x2f20f9c077155065!8m2!3d49.027934!4d12.137797!16s%2Fg%2F11ms93zrfy!19sChIJO6H69IrBn0cRZVAVd8D5IC8?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Architekturbüro Pongratz Regensburg</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Dr.-Gessler-Straße 16, 93051 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 42830</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.architekturbuero-pongratz.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekturb%C3%BCro+Pongratz+Regensburg/data=!4m7!3m6!1s0x479fc0e459b33939:0xec7c0897acb24831!8m2!3d49.006234!4d12.063848!16s%2Fg%2F1tvw3ybm!19sChIJOTmzWeTAn0cRMUiyrJcIfOw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>B&amp;O Bau Bayern GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Građevinska tvrtka</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Bajuwarenstraße 2e, 93053 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 8061 28020</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://buo.de/bau/unternehmen/bo-bau-bayern-gmbh/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/B%26O+Bau+Bayern+GmbH/data=!4m7!3m6!1s0x479fc163de76e6b7:0xc1c6a452be031f05!8m2!3d49.000671!4d12.123976!16s%2Fg%2F11vk2rbydj!19sChIJt-Z23mPBn0cRBR8DvlKkxsE?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>OTH Regensburg Fakultät Architektur</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Akademski odjel</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Galgenbergstraße 32, 93053 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 9431180</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oth-regensburg.de/fakultaeten/architektur.html</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/OTH+Regensburg+Fakult%C3%A4t+Architektur/data=!4m7!3m6!1s0x479fc0f89a4fa4f3:0xc64b16cbc2ff1e0e!8m2!3d49.0025387!4d12.0984498!16s%2Fg%2F11gz8vjvq!19sChIJ86RPmvjAn0cRDh7_wssWS8Y?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="71.25" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Doemges Architekten AG</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>
+Budapester Str. 4, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 992060</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.doemges.ag/</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Doemges+Architekten+AG/data=!4m7!3m6!1s0x479fc0e1fd8473cd:0x5ca6394ae9d138dc!8m2!3d49.0188952!4d12.121771!16s%2Fg%2F1tff20fc!19sChIJzXOE_eHAn0cR3DjR6Uo5plw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="71.25" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Modellbau Münster</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Modelarstvo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>
+Wienburgstraße 207, 48159 Münster, Njemačka</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>http://www.modellbaumuenster.de/</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Modellbau+M%C3%BCnster/data=!4m7!3m6!1s0x47b9bb4d5786be75:0xfeae827fffd5d7fc!8m2!3d51.9870146!4d7.6186279!16s%2Fg%2F11hyk8jvlz!19sChIJdb6GV027uUcR_NfV_3-Crv4?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="85.5" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>beta-planungsteam gmbh</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>
+Gutenbergstraße 5C, 93051 Regensburg-Kumpfmühl-Ziegetsdorf-Neuprüll, Njemačka</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 5995400</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>http://www.beta-planungsteam.de/</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/beta-planungsteam+gmbh/data=!4m7!3m6!1s0x479fc10591d55a17:0x425fd896a6ee5f0d!8m2!3d49.0082058!4d12.0891124!16s%2Fg%2F1hc7cyrz0!19sChIJF1rVkQXBn0cRDV_uppbYX0I?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:43</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q5"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="doslovmarko@gmail.com" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="doslovmarko@gmail.com" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="doslovmarko@gmail.com" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="doslovmarko@gmail.com" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Baustellensicherung Regensburg</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Savjetnik za gradnju</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Im Gewerbepark, 93059 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 569591137</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://baustellensicherung-regensburg.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Baustellensicherung+Regensburg/data=!4m7!3m6!1s0x479fc13919cd3d7f:0x586c1a433870f145!8m2!3d49.03022!4d12.1263832!16s%2Fg%2F11zb8151n4!19sChIJfz3NGTnBn0cRRfFwOEMabFg?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="85.5" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>WeberHaus GmbH &amp; Co. KG Bauforum Regensburg</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Graditelj modularnih kuća</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>
+Konrad-Adenauer-Allee 30, 93051 Regensburg-Kumpfmühl-Ziegetsdorf-Neuprüll, Njemačka</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 464150</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.weberhaus.de/erleben/bauforen/regensburg/?utm_source=GMB&amp;utm_medium=LINK&amp;utm_campaign=BAUFOREN&amp;utm_id=BAUFOREN</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/WeberHaus+GmbH+%26+Co.+KG+Bauforum+Regensburg/data=!4m7!3m6!1s0x479fc18af50643bf:0xc455b47ceff73aaf!8m2!3d48.9978988!4d12.0700468!16s%2Fg%2F1tkjk5sp!19sChIJv0MG9YrBn0cRrzr373y0VcQ?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="71.25" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>baufiXperten GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Hipotekarni agent</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>
+Nußbergerstraße 6 B, 93059 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 46165010</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>http://www.baufixperten.de/</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/baufiXperten+GmbH/data=!4m7!3m6!1s0x479fc1bc06c8c1e9:0xacbb1c18454fd8b7!8m2!3d49.0283777!4d12.106409!16s%2Fg%2F11dxdyyd90!19sChIJ6cHIBrzBn0cRt9hPRRgcu6w?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:43</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="85.5" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>VPB-Regionalbüro Regensburg</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Građevinski inspektor</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>
+Spitalstraße 5, 93138 Lappersdorf-Kareth, Njemačka</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 46105600</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.vpb.de/regionalbueros/regensburg</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/VPB-Regionalb%C3%BCro+Regensburg/data=!4m7!3m6!1s0x479fc210208f32f1:0x3da397452b1b57!8m2!3d49.04138!4d12.08979!16s%2Fg%2F1wrtbvxs!19sChIJ8TKPIBDCn0cRVxsrRZejPQA?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:43</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="71.25" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BaufiBude</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Financijski savjetnik</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>
+Donaustaufer Str. 162, 93059 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>
++49 1512 9856097</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.baufibude.de/</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/BaufiBude/data=!4m7!3m6!1s0x479fc151cd977527:0x70ef3800496f283f!8m2!3d49.0283304!4d12.1266844!16s%2Fg%2F11zh2hgdhp!19sChIJJ3WXzVHBn0cRPyhvSQA473A?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:43</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q6"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="doslovmarko@gmail.com" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="doslovmarko@gmail.com" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="doslovmarko@gmail.com" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="doslovmarko@gmail.com" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>PURE GRUPPE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitektonska tvrtka</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Watmarkt 5, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 5861240000</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>bojan.mikulic@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.puregruppe.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/PURE+GRUPPE/data=!4m7!3m6!1s0x479fc1a12bb878b3:0x811be9b90bc55a40!8m2!3d49.0201388!4d12.0965148!16s%2Fg%2F1td52fgl!19sChIJs3i4K6HBn0cRQFrFC7npG4E?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="85.5" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Architekturbüro Pongratz Regensburg</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>
+Dr.-Gessler-Straße 16, 93051 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 42830</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.architekturbuero-pongratz.de/</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekturb%C3%BCro+Pongratz+Regensburg/data=!4m7!3m6!1s0x479fc0e459b33939:0xec7c0897acb24831!8m2!3d49.006234!4d12.063848!16s%2Fg%2F1tvw3ybm!19sChIJOTmzWeTAn0cRMUiyrJcIfOw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="85.5" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>bildstaerke | franz außerstorfer</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>
+An d. Hülling 2, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>
++49 1514 1267387</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>http://www.bildstaerke.de/</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/bildstaerke+%7C+franz+au%C3%9Ferstorfer/data=!4m7!3m6!1s0x479fc1a7ddea030f:0xea4e9e739b56fd3e!8m2!3d49.016044!4d12.09433!16s%2Fg%2F1q64jnhp9!19sChIJDwPq3afBn0cRPv1Wm3OeTuo?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="85.5" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>KRANZ - Innenarchitekt Regensburg für innovative Räume</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Dizajner interijera</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>
+Johanna-Kinkel-Straße 2, 93049 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 396440</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>https://kranz-buero.de/innenarchitekt-regensburg/</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/KRANZ+-+Innenarchitekt+Regensburg+f%C3%BCr+innovative+R%C3%A4ume/data=!4m7!3m6!1s0x479fc0f16e7aa28f:0x79102993edd22fe0!8m2!3d49.0128371!4d12.0740564!16s%2Fg%2F1tjcnfvk!19sChIJj6J6bvHAn0cR4C_S7ZMpEHk?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="71.25" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Doemges Architekten AG</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>
+Budapester Str. 4, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 992060</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.doemges.ag/</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Doemges+Architekten+AG/data=!4m7!3m6!1s0x479fc0e1fd8473cd:0x5ca6394ae9d138dc!8m2!3d49.0188952!4d12.121771!16s%2Fg%2F1tff20fc!19sChIJzXOE_eHAn0cR3DjR6Uo5plw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="85.5" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>beta-planungsteam gmbh</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>
+Gutenbergstraße 5C, 93051 Regensburg-Kumpfmühl-Ziegetsdorf-Neuprüll, Njemačka</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 5995400</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>http://www.beta-planungsteam.de/</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/beta-planungsteam+gmbh/data=!4m7!3m6!1s0x479fc10591d55a17:0x425fd896a6ee5f0d!8m2!3d49.0082058!4d12.0891124!16s%2Fg%2F1hc7cyrz0!19sChIJF1rVkQXBn0cRDV_uppbYX0I?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="71.25" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Basqué Et Partner</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>
+Theodor-Storm-Straße 21a, 93051 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 21986</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>http://www.basque.de/</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Basqu%C3%A9+Et+Partner/data=!4m7!3m6!1s0x479fc1098665a817:0x436e0301530c10d1!8m2!3d48.99578!4d12.08032!16s%2Fg%2F1w0sbw60!19sChIJF6hlhgnBn0cR0RAMUwEDbkM?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="85.5" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>raumstaerke konzept|planung|realisierung</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>
+An d. Hülling 2, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>
++49 941 46183616</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.raumstaerke.de/</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/raumstaerke+konzept%7Cplanung%7Crealisierung/data=!4m7!3m6!1s0x479fc1a7dd04c5b5:0xb3c12b02de84d230!8m2!3d49.0160444!4d12.0943298!16s%2Fg%2F11f03tzn25!19sChIJtcUE3afBn0cRMNKE3gIrwbM?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q9"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="doslovmarko@gmail.com" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="doslovmarko@gmail.com" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="doslovmarko@gmail.com" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="doslovmarko@gmail.com" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="doslovmarko@gmail.com" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" display="doslovmarko@gmail.com" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" display="doslovmarko@gmail.com" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId23"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Architekturbüro Pongratz Regensburg</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Dr.-Gessler-Straße 16, 93051 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 42830</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.architekturbuero-pongratz.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekturb%C3%BCro+Pongratz+Regensburg/data=!4m7!3m6!1s0x479fc0e459b33939:0xec7c0897acb24831!8m2!3d49.006234!4d12.063848!16s%2Fg%2F1tvw3ybm!19sChIJOTmzWeTAn0cRMUiyrJcIfOw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="85.5" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>bildstaerke | franz außerstorfer</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>
+An d. Hülling 2, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>
++49 1514 1267387</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>http://www.bildstaerke.de/</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/bildstaerke+%7C+franz+au%C3%9Ferstorfer/data=!4m7!3m6!1s0x479fc1a7ddea030f:0xea4e9e739b56fd3e!8m2!3d49.016044!4d12.09433!16s%2Fg%2F1q64jnhp9!19sChIJDwPq3afBn0cRPv1Wm3OeTuo?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="71.25" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Huber Architekten GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>
+Dechbettener Str. 10, 93049 Regensburg-Westenviertel, Njemačka</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 595810</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>http://www.archhu.de/</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Huber+Architekten+GmbH/data=!4m7!3m6!1s0x479fc1a5c344f023:0x363bdbfeba440210!8m2!3d49.0171277!4d12.0830257!16s%2Fg%2F1tg5ymqj!19sChIJI_BEw6XBn0cREAJEuv7bOzY?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="85.5" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>johannsraum Architekten Bock &amp; Emminger PartGmbB</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>
+Obermünsterstraße 9, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>https://johannsraum.de/imprint/</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/johannsraum+Architekten+Bock+%26+Emminger+PartGmbB/data=!4m7!3m6!1s0x479fc1d04f9e24ab:0xd9304347eea87045!8m2!3d49.0167728!4d12.0957967!16s%2Fg%2F11qfygqfwg!19sChIJqySeT9DBn0cRRXCo7kdDMNk?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="71.25" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Architekt Heitzer</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>
+Galgenbergstraße 21, 93053 Regensburg-Galgenberg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 7994444</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://architektheitzer.de/</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Architekt+Heitzer/data=!4m7!3m6!1s0x479fc1b02ffedeb7:0xa6b971e2b3c898ae!8m2!3d49.0072517!4d12.1005756!16s%2Fg%2F1thkw85n!19sChIJt97-L7DBn0cRrpjIs-JxuaY?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:43</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q6"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="doslovmarko@gmail.com" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" display="doslovmarko@gmail.com" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" display="doslovmarko@gmail.com" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" display="doslovmarko@gmail.com" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="doslovmarko@gmail.com" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Doemges Architekten AG</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Budapester Str. 4, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 992060</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.doemges.ag/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Doemges+Architekten+AG/data=!4m7!3m6!1s0x479fc0e1fd8473cd:0x5ca6394ae9d138dc!8m2!3d49.0188952!4d12.121771!16s%2Fg%2F1tff20fc!19sChIJzXOE_eHAn0cR3DjR6Uo5plw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Doemges Architekten AG</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitekt</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Budapester Str. 4, 93055 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 992060</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.doemges.ag/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Doemges+Architekten+AG/data=!4m7!3m6!1s0x479fc0e1fd8473cd:0x5ca6394ae9d138dc!8m2!3d49.0188952!4d12.121771!16s%2Fg%2F1tff20fc!19sChIJzXOE_eHAn0cR3DjR6Uo5plw?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Baustellensicherung Regensburg</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Savjetnik za gradnju</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Im Gewerbepark, 93059 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 569591137</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://baustellensicherung-regensburg.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Baustellensicherung+Regensburg/data=!4m7!3m6!1s0x479fc13919cd3d7f:0x586c1a433870f145!8m2!3d49.03022!4d12.1263832!16s%2Fg%2F11zb8151n4!19sChIJfz3NGTnBn0cRRfFwOEMabFg?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>PURE GRUPPE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Arhitektonska tvrtka</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Watmarkt 5, 93047 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 5861240000</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.puregruppe.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/PURE+GRUPPE/data=!4m7!3m6!1s0x479fc1a12bb878b3:0x811be9b90bc55a40!8m2!3d49.0201388!4d12.0965148!16s%2Fg%2F1td52fgl!19sChIJs3i4K6HBn0cRQFrFC7npG4E?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:41</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Br.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorija</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adresa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Web stranica</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Radno vrijeme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ocjena</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recenzije</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Plus Code</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Google Maps URL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Datum scrape</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Pozvano (DA/NE)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zainteresovan (DA/NE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="71.25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>OLYMP Haus GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Građevinska tvrtka</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>
+Sie finden uns im 8. OG, Prüfeninger Str. 35, 93049 Regensburg, Njemačka</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>
++49 941 46394660</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>doslovmarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>http://www.olymp-group.de/</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/OLYMP+Haus+GmbH/data=!4m7!3m6!1s0x479fc311a7cd840d:0x95b16f71ed24a91d!8m2!3d49.0169667!4d12.0772104!16s%2Fg%2F11d_c00d_w!19sChIJDYTNpxHDn0cRHakk7XFvsZU?authuser=0&amp;hl=hr&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:42</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>